--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A131BC96-8EDD-477C-B71F-67658558AAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476710BC-0AAA-4407-BDD2-93F40B5887ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -144,6 +144,22 @@
   </si>
   <si>
     <t>Um nível de dificuldade para iniciantes, pensado para que até quem não é bom em jogos de ação 3D possa se divertir.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationSizeRussian</t>
+  </si>
+  <si>
+    <t>Уровень для новичков: играть будет интересно даже тем, кому непросто даются 3D-экшены.</t>
+  </si>
+  <si>
+    <t>Непростой уровень для опытных игроков.</t>
+  </si>
+  <si>
+    <t>Уровень для мастеров: сложно будет даже тем, кто хорошо играет в 3D-экшены. Вы пожалеете, что решились на это.</t>
+  </si>
+  <si>
+    <t>explanationRussian</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -492,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
@@ -507,9 +523,11 @@
     <col min="11" max="11" width="21.25" customWidth="1"/>
     <col min="12" max="12" width="22.25" customWidth="1"/>
     <col min="13" max="13" width="24.375" customWidth="1"/>
+    <col min="14" max="14" width="29.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,13 +567,19 @@
       <c r="M1" t="s">
         <v>27</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="131.25">
+    <row r="3" spans="1:15" ht="131.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -595,8 +619,14 @@
       <c r="M3">
         <v>10</v>
       </c>
+      <c r="N3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="56.25">
+    <row r="4" spans="1:15" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -636,8 +666,14 @@
       <c r="M4">
         <v>14</v>
       </c>
+      <c r="N4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="147.75" customHeight="1">
+    <row r="5" spans="1:15" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -677,8 +713,14 @@
       <c r="M5">
         <v>14</v>
       </c>
+      <c r="N5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476710BC-0AAA-4407-BDD2-93F40B5887ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A343CB27-4E46-4593-9CFA-4A2D0E44AA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -161,6 +161,21 @@
   <si>
     <t>explanationRussian</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>explanationGerman</t>
+  </si>
+  <si>
+    <t>explanationSizeGerman</t>
+  </si>
+  <si>
+    <t>Ein einsteigerfreundlicher Schwierigkeitsgrad, der auch Spielern Spaß macht, die mit 3D-Action nicht so vertraut sind.</t>
+  </si>
+  <si>
+    <t>Ein fordernder Schwierigkeitsgrad für fortgeschrittene Spieler.</t>
+  </si>
+  <si>
+    <t>Ein Schwierigkeitsgrad für Profis, den selbst geübte 3D-Action-Spieler als schwer empfinden. Du wirst bereuen, es versucht zu haben.</t>
   </si>
 </sst>
 </file>
@@ -508,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
@@ -524,10 +539,11 @@
     <col min="12" max="12" width="22.25" customWidth="1"/>
     <col min="13" max="13" width="24.375" customWidth="1"/>
     <col min="14" max="14" width="29.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -573,13 +589,19 @@
       <c r="O1" t="s">
         <v>31</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="131.25">
+    <row r="3" spans="1:17" ht="131.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -625,8 +647,14 @@
       <c r="O3">
         <v>10</v>
       </c>
+      <c r="P3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="56.25">
+    <row r="4" spans="1:17" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -672,8 +700,14 @@
       <c r="O4">
         <v>14</v>
       </c>
+      <c r="P4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" ht="147.75" customHeight="1">
+    <row r="5" spans="1:17" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -719,8 +753,14 @@
       <c r="O5">
         <v>14</v>
       </c>
+      <c r="P5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A343CB27-4E46-4593-9CFA-4A2D0E44AA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CC5393-EEEE-42C7-9655-DBA0F8733782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -176,6 +176,21 @@
   </si>
   <si>
     <t>Ein Schwierigkeitsgrad für Profis, den selbst geübte 3D-Action-Spieler als schwer empfinden. Du wirst bereuen, es versucht zu haben.</t>
+  </si>
+  <si>
+    <t>explanationFrench</t>
+  </si>
+  <si>
+    <t>explanationSizeFrench</t>
+  </si>
+  <si>
+    <t>Une difficulté pour débutants, agréable même pour ceux qui ne sont pas à l'aise avec les jeux d'action 3D.</t>
+  </si>
+  <si>
+    <t>Une difficulté corsée pour joueurs confirmés.</t>
+  </si>
+  <si>
+    <t>Une difficulté pour experts, que même les habitués de l'action 3D trouveront redoutable. Vous regretterez d'avoir essayé.</t>
   </si>
 </sst>
 </file>
@@ -523,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
@@ -541,9 +556,11 @@
     <col min="14" max="14" width="29.25" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="23.125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19" ht="37.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -595,13 +612,19 @@
       <c r="Q1" t="s">
         <v>37</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="131.25">
+    <row r="3" spans="1:19" ht="262.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -653,8 +676,14 @@
       <c r="Q3">
         <v>10</v>
       </c>
+      <c r="R3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" ht="56.25">
+    <row r="4" spans="1:19" ht="131.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -706,8 +735,14 @@
       <c r="Q4">
         <v>14</v>
       </c>
+      <c r="R4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="147.75" customHeight="1">
+    <row r="5" spans="1:19" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -759,8 +794,14 @@
       <c r="Q5">
         <v>14</v>
       </c>
+      <c r="R5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>

--- a/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
+++ b/Assets/Originals/Excels/DifficultyLevelExplanation/DifficultyLevelExplanation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\DifficultyLevelExplanation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CC5393-EEEE-42C7-9655-DBA0F8733782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781F8795-015F-4C70-AB90-27F1102E6AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -191,6 +191,21 @@
   </si>
   <si>
     <t>Une difficulté pour experts, que même les habitués de l'action 3D trouveront redoutable. Vous regretterez d'avoir essayé.</t>
+  </si>
+  <si>
+    <t>explanationTurkish</t>
+  </si>
+  <si>
+    <t>explanationSizeTurkish</t>
+  </si>
+  <si>
+    <t>3D aksiyon oyunlarında zorlananların bile keyif alabileceği, yeni başlayanlara uygun bir zorluk seviyesi.</t>
+  </si>
+  <si>
+    <t>Orta seviye oyuncular için zorlayıcı bir seviye.</t>
+  </si>
+  <si>
+    <t>3D aksiyonda usta olanların bile zorlanacağı, ileri seviye oyunculara yönelik bir zorluk. Denediğine pişman olacaksın.</t>
   </si>
 </sst>
 </file>
@@ -538,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="57.375" style="1" customWidth="1"/>
@@ -558,9 +573,11 @@
     <col min="17" max="17" width="22.875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="37.5">
+    <row r="1" spans="1:21" ht="56.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -618,13 +635,19 @@
       <c r="S1" t="s">
         <v>42</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="262.5">
+    <row r="3" spans="1:21" ht="262.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -682,8 +705,14 @@
       <c r="S3">
         <v>10</v>
       </c>
+      <c r="T3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:19" ht="131.25">
+    <row r="4" spans="1:21" ht="131.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -741,8 +770,14 @@
       <c r="S4">
         <v>14</v>
       </c>
+      <c r="T4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" ht="147.75" customHeight="1">
+    <row r="5" spans="1:21" ht="147.75" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -800,8 +835,14 @@
       <c r="S5">
         <v>14</v>
       </c>
+      <c r="T5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>4</v>
       </c>
